--- a/30_Threshold_OUTPUT/direct_P0A7C2_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/30_Threshold_OUTPUT/direct_P0A7C2_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.9674130347860855</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.5355857656937225</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -586,6 +601,11 @@
       <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.9968012794882047</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -664,6 +689,11 @@
       <c r="I6" t="n">
         <v>0.9290283886445422</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -702,6 +732,11 @@
       </c>
       <c r="I7" t="n">
         <v>0.998000799680128</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/30_Threshold_OUTPUT/direct_P0A7C2_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/30_Threshold_OUTPUT/direct_P0A7C2_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -606,6 +617,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -650,6 +664,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -694,6 +711,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -737,6 +757,9 @@
         <is>
           <t>Confirmed DR</t>
         </is>
+      </c>
+      <c r="K7" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
